--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,109 +55,61 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>В0235РС</t>
   </si>
   <si>
+    <t>В8992ВР</t>
+  </si>
+  <si>
+    <t>В7240ВР</t>
+  </si>
+  <si>
     <t>В0233РС</t>
   </si>
   <si>
-    <t>В7240ВР</t>
-  </si>
-  <si>
-    <t>В8992ВР</t>
-  </si>
-  <si>
     <t>78970155027720543</t>
   </si>
   <si>
+    <t>78970155027720550</t>
+  </si>
+  <si>
+    <t>78970155027720568</t>
+  </si>
+  <si>
     <t>78970155027720535</t>
   </si>
   <si>
-    <t>78970155027720568</t>
-  </si>
-  <si>
-    <t>78970155027720550</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:39:00</t>
-  </si>
-  <si>
-    <t>08:26:00</t>
-  </si>
-  <si>
-    <t>17:30:00</t>
-  </si>
-  <si>
-    <t>14:52:00</t>
-  </si>
-  <si>
-    <t>08:34:00</t>
-  </si>
-  <si>
-    <t>10:37:00</t>
-  </si>
-  <si>
-    <t>08:33:00</t>
-  </si>
-  <si>
-    <t>08:35:00</t>
-  </si>
-  <si>
-    <t>09:04:00</t>
-  </si>
-  <si>
-    <t>17:20:00</t>
-  </si>
-  <si>
-    <t>3236525854 3236525854</t>
-  </si>
-  <si>
-    <t>3236629989 3236629989</t>
-  </si>
-  <si>
-    <t>3236657776 3236657776</t>
-  </si>
-  <si>
-    <t>3236716718 3236716718</t>
-  </si>
-  <si>
-    <t>3236848480 3236848480</t>
-  </si>
-  <si>
-    <t>3236906663 3236906663</t>
-  </si>
-  <si>
-    <t>3236943900 3236943900</t>
-  </si>
-  <si>
-    <t>3236954827 3236954827</t>
-  </si>
-  <si>
-    <t>3237126478 3237126478</t>
-  </si>
-  <si>
-    <t>3237213770 3237213770</t>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>13:23</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>10:33</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -583,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -592,17 +541,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -642,192 +590,177 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>28</v>
+      <c r="G2" s="1">
+        <v>1.58</v>
       </c>
       <c r="H2" s="1">
-        <v>1.53</v>
+        <v>31.6</v>
       </c>
       <c r="I2" s="1">
-        <v>30.6</v>
+        <v>1.61</v>
       </c>
       <c r="J2" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
-        <v>31.2</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
+        <v>32.2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>169303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46254</v>
+        <v>46268</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H3" s="1">
+        <v>31.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J3" s="1">
+        <v>32.2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>170130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>29.92</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H4" s="1">
+        <v>19.747</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J4" s="1">
+        <v>20.046</v>
+      </c>
+      <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
+      <c r="L4">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46254</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="M4">
+        <v>172260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="I4" s="1">
-        <v>52.7</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K4" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H5" s="1">
+        <v>32</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J5" s="1">
+        <v>32.6</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46255</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="M5">
+        <v>149102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>33.86</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>22.009</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
-        <v>22.348</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46258</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -836,347 +769,165 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
+        <v>37.1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.66</v>
       </c>
       <c r="H6" s="1">
-        <v>1.54</v>
+        <v>24.486</v>
       </c>
       <c r="I6" s="1">
-        <v>30.8</v>
+        <v>0.67</v>
       </c>
       <c r="J6" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="L6" t="s">
+        <v>24.857</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>300328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="H7" s="1">
+        <v>57.05</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J7" s="1">
+        <v>58.1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>174142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46259</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7">
+        <v>95</v>
+      </c>
+      <c r="C12" s="8">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.60263</v>
+      </c>
+      <c r="E12" s="7">
+        <v>152.25</v>
+      </c>
+      <c r="F12" s="7">
+        <v>155.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>31.33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I7" s="1">
-        <v>20.364</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="B13" s="7">
+        <v>67.02</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9">
         <v>0.66</v>
       </c>
-      <c r="K7" s="1">
-        <v>20.678</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3">
-        <v>46260</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="I8" s="1">
-        <v>31</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K8" s="1">
-        <v>31.6</v>
-      </c>
-      <c r="L8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3">
-        <v>46260</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="I9" s="1">
-        <v>15.5</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15.8</v>
-      </c>
-      <c r="L9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="3">
-        <v>46265</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10">
-        <v>32.24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I10" s="1">
-        <v>20.956</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K10" s="1">
-        <v>21.278</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="E13" s="7">
+        <v>44.23</v>
+      </c>
+      <c r="F13" s="7">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="3">
-        <v>46265</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11">
-        <v>59</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="I11" s="1">
-        <v>93.81</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="K11" s="1">
-        <v>95.58</v>
-      </c>
-      <c r="L11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="7">
-        <v>183</v>
-      </c>
-      <c r="C16" s="8">
-        <v>7</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1.55852</v>
-      </c>
-      <c r="E16" s="7">
-        <v>285.21</v>
-      </c>
-      <c r="F16" s="7">
-        <v>290.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="7">
-        <v>97.43000000000001</v>
-      </c>
-      <c r="C17" s="8">
-        <v>3</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0.64999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>63.33</v>
-      </c>
-      <c r="F17" s="7">
-        <v>64.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="11">
-        <v>280.43</v>
-      </c>
-      <c r="C18" s="12">
-        <v>10</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="11">
-        <v>348.54</v>
-      </c>
-      <c r="F18" s="11">
-        <v>355</v>
+      <c r="B14" s="11">
+        <v>162.02</v>
+      </c>
+      <c r="C14" s="12">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="11">
+        <v>196.48</v>
+      </c>
+      <c r="F14" s="11">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
